--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/OLEO 15_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/OLEO 15_02.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t> </t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/OLEO 15_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/OLEO 15_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -553,7 +532,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,17 +544,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OLEO SHELL 20W 30</t>
+          <t>OLEO SHELL 20W 50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
@@ -586,20 +559,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7898913974531</t>
+          <t>7891344018164</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OLEO BULUB 10W 20</t>
+          <t>OLEO LUBRAX 20W 50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -607,20 +579,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t> </t>
+          <t>7891281009317</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t> </t>
+          <t>OLEO CASTROL 20W 50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7896636550827</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OLEO MOBIL 10W 30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
